--- a/Team-Data/2012-13/12-6-2012-13.xlsx
+++ b/Team-Data/2012-13/12-6-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
         <v>6</v>
@@ -757,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -784,10 +851,10 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>9</v>
@@ -957,7 +1024,7 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1115,7 +1182,7 @@
         <v>8</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>21</v>
@@ -1139,7 +1206,7 @@
         <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>25</v>
@@ -1154,7 +1221,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
         <v>4</v>
@@ -1178,7 +1245,7 @@
         <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1330,7 +1397,7 @@
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1479,7 +1546,7 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>24</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1661,7 +1728,7 @@
         <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>23</v>
@@ -1673,7 +1740,7 @@
         <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM7" t="n">
         <v>6</v>
@@ -1706,7 +1773,7 @@
         <v>23</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1715,10 +1782,10 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -1753,67 +1820,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.474</v>
+        <v>0.444</v>
       </c>
       <c r="H8" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I8" t="n">
         <v>36.6</v>
       </c>
       <c r="J8" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.385</v>
+        <v>0.387</v>
       </c>
       <c r="O8" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S8" t="n">
         <v>31.9</v>
       </c>
       <c r="T8" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W8" t="n">
         <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y8" t="n">
         <v>4.4</v>
@@ -1828,34 +1895,34 @@
         <v>98.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AF8" t="n">
         <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
         <v>16</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
@@ -1873,7 +1940,7 @@
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS8" t="n">
         <v>9</v>
@@ -1882,10 +1949,10 @@
         <v>19</v>
       </c>
       <c r="AU8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
@@ -2025,10 +2092,10 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2295,7 @@
         <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
         <v>9</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2416,7 +2483,7 @@
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
         <v>15</v>
@@ -2428,7 +2495,7 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>1.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>14</v>
@@ -2598,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
         <v>4</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
         <v>26</v>
@@ -2631,7 +2698,7 @@
         <v>23</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>9</v>
@@ -2777,7 +2844,7 @@
         <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2935,10 +3002,10 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>24</v>
@@ -2968,7 +3035,7 @@
         <v>23</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
         <v>24</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3129,7 +3196,7 @@
         <v>7</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>4</v>
@@ -3180,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>8.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>1</v>
@@ -3362,7 +3429,7 @@
         <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -3391,91 +3458,91 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.706</v>
+        <v>0.75</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
       <c r="J17" t="n">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.489</v>
+        <v>0.493</v>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M17" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.411</v>
+        <v>0.413</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="S17" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="T17" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="n">
         <v>13.8</v>
       </c>
       <c r="W17" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
         <v>3.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.6</v>
+        <v>104.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>5</v>
@@ -3484,37 +3551,37 @@
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
         <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
         <v>29</v>
@@ -3535,16 +3602,16 @@
         <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3718,19 @@
         <v>-2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>6</v>
@@ -3702,13 +3769,13 @@
         <v>18</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
         <v>6</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3717,10 +3784,10 @@
         <v>3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>0.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
         <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
@@ -3887,7 +3954,7 @@
         <v>23</v>
       </c>
       <c r="AV19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4060,13 +4127,13 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.778</v>
+        <v>0.765</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J21" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.455</v>
       </c>
       <c r="L21" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="M21" t="n">
-        <v>29.7</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
         <v>0.407</v>
       </c>
       <c r="O21" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="P21" t="n">
         <v>20.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.766</v>
+        <v>0.773</v>
       </c>
       <c r="R21" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="U21" t="n">
         <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
         <v>9.1</v>
@@ -4188,16 +4255,16 @@
         <v>18.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>103.2</v>
+        <v>102.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -4209,13 +4276,13 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
         <v>9</v>
@@ -4236,16 +4303,16 @@
         <v>26</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU21" t="n">
         <v>25</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>9</v>
@@ -4400,7 +4467,7 @@
         <v>30</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>22</v>
@@ -4573,7 +4640,7 @@
         <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>13</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>9</v>
@@ -4755,13 +4822,13 @@
         <v>10</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>22</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -4847,100 +4914,100 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
         <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.35</v>
+        <v>0.368</v>
       </c>
       <c r="H25" t="n">
         <v>48.8</v>
       </c>
       <c r="I25" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="J25" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L25" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M25" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O25" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P25" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R25" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S25" t="n">
         <v>29.1</v>
       </c>
       <c r="T25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U25" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V25" t="n">
         <v>14.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z25" t="n">
         <v>21.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.5</v>
+        <v>-4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ25" t="n">
         <v>2</v>
@@ -4958,10 +5025,10 @@
         <v>22</v>
       </c>
       <c r="AO25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP25" t="n">
         <v>24</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>21</v>
@@ -4982,7 +5049,7 @@
         <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -4994,10 +5061,10 @@
         <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC25" t="n">
         <v>24</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>-3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
         <v>22</v>
@@ -5125,7 +5192,7 @@
         <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK26" t="n">
         <v>23</v>
@@ -5143,7 +5210,7 @@
         <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>20</v>
@@ -5155,7 +5222,7 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5164,7 +5231,7 @@
         <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX26" t="n">
         <v>20</v>
@@ -5179,7 +5246,7 @@
         <v>15</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>23</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5307,7 +5374,7 @@
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
@@ -5322,10 +5389,10 @@
         <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5486,7 +5553,7 @@
         <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
@@ -5495,7 +5562,7 @@
         <v>5</v>
       </c>
       <c r="AL28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-5</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>28</v>
@@ -5680,7 +5747,7 @@
         <v>12</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN29" t="n">
         <v>18</v>
@@ -5689,7 +5756,7 @@
         <v>10</v>
       </c>
       <c r="AP29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ29" t="n">
         <v>8</v>
@@ -5698,7 +5765,7 @@
         <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT29" t="n">
         <v>23</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -5847,16 +5914,16 @@
         <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI30" t="n">
         <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
@@ -6053,7 +6120,7 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-6-2012-13</t>
+          <t>2012-12-06</t>
         </is>
       </c>
     </row>
